--- a/site/exports/sysu-history-zhuhai.xlsx
+++ b/site/exports/sysu-history-zhuhai.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；中大归属仅官方索引，个人页正文与实时在职未核；中山大学历史学系（珠海）仅为官方索引抽样关联，未核当前任职；历史职业事实另有正文来源。</t>
+          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；中大归属仅官方索引，个人页正文与实时在职未核；中山大学历史学系（珠海）仅为官方索引抽样关联，未核当前任职；历史职业事实另有正文来源。；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；中大归属仅官方索引，个人页正文与实时在职未核；中山大学历史学系（珠海）仅为官方索引抽样关联，未核当前任职；历史职业事实另有正文来源。</t>
+          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；中大归属仅官方索引，个人页正文与实时在职未核；中山大学历史学系（珠海）仅为官方索引抽样关联，未核当前任职；历史职业事实另有正文来源。；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；中大归属仅官方索引，个人页正文与实时在职未核；中山大学历史学系（珠海）仅为官方索引抽样关联，未核当前任职；历史职业事实另有正文来源。</t>
+          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；中大归属仅官方索引，个人页正文与实时在职未核；中山大学历史学系（珠海）仅为官方索引抽样关联，未核当前任职；历史职业事实另有正文来源。；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
